--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.1043,0.0334,0.8485,0.0004</t>
-  </si>
-  <si>
-    <t>0.1006,0.0144,0.8924,0.0010</t>
-  </si>
-  <si>
-    <t>0.3368,0.0406,0.5746,0.0023</t>
-  </si>
-  <si>
-    <t>0.1276,0.0133,0.8662,0.0007</t>
-  </si>
-  <si>
-    <t>0.5033,0.5161,0.0205,0.0004</t>
-  </si>
-  <si>
-    <t>0.3641,0.6488,0.0268,0.0005</t>
-  </si>
-  <si>
-    <t>0.2833,0.7271,0.0276,0.0005</t>
-  </si>
-  <si>
-    <t>0.4057,0.6160,0.0219,0.0004</t>
-  </si>
-  <si>
-    <t>0.3955,0.6548,0.0201,0.0004</t>
-  </si>
-  <si>
-    <t>0.3063,0.6946,0.0273,0.0005</t>
-  </si>
-  <si>
-    <t>0.4790,0.5272,0.0250,0.0004</t>
-  </si>
-  <si>
-    <t>0.4861,0.5321,0.0235,0.0004</t>
-  </si>
-  <si>
-    <t>0.0538,0.0485,0.9038,0.0004</t>
-  </si>
-  <si>
-    <t>0.0181,0.0213,0.9689,0.0001</t>
-  </si>
-  <si>
-    <t>0.0085,0.0329,0.9812,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0239,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.0647,0.0170,0.9129,0.0002</t>
-  </si>
-  <si>
-    <t>0.0062,0.9845,0.0345,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.9833,0.0669,0.0000</t>
-  </si>
-  <si>
-    <t>0.0135,0.9495,0.1182,0.0001</t>
-  </si>
-  <si>
-    <t>0.0051,0.9854,0.0397,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9952,0.0292,0.0000</t>
-  </si>
-  <si>
-    <t>0.0145,0.0147,0.9801,0.0001</t>
-  </si>
-  <si>
-    <t>0.0074,0.0289,0.9870,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0049,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0046,0.0149,0.9921,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0127,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.0253,0.9924,0.0001</t>
-  </si>
-  <si>
-    <t>0.0025,0.0062,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.1930,0.3187,0.4005,0.0009</t>
-  </si>
-  <si>
-    <t>0.0798,0.0854,0.8179,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0061,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0135,0.7460,0.5636,0.0002</t>
-  </si>
-  <si>
-    <t>0.2017,0.1885,0.5310,0.0011</t>
-  </si>
-  <si>
-    <t>0.0890,0.1492,0.7556,0.0005</t>
-  </si>
-  <si>
-    <t>0.1004,0.8222,0.0853,0.0005</t>
-  </si>
-  <si>
-    <t>0.0233,0.8639,0.2769,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9344,0.9185,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.2476,0.9906,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.4313,0.9924,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0127,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.7159,0.9810,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9956,0.1961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0527,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0487,0.0682,0.8986,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.9924,0.1185,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.9637,0.3981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9985,0.0428,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.5458,0.9876,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.1461,0.9969,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0089,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0024,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0018,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.0411,0.9934,0.0000</t>
-  </si>
-  <si>
-    <t>0.1799,0.8038,0.0355,0.0004</t>
-  </si>
-  <si>
-    <t>0.1963,0.1777,0.5534,0.0009</t>
-  </si>
-  <si>
-    <t>0.2395,0.7319,0.0349,0.0004</t>
-  </si>
-  <si>
-    <t>0.0076,0.0488,0.9801,0.0001</t>
-  </si>
-  <si>
-    <t>0.4801,0.3757,0.0830,0.0011</t>
-  </si>
-  <si>
-    <t>0.2700,0.7345,0.0319,0.0005</t>
-  </si>
-  <si>
-    <t>0.2409,0.6914,0.0601,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.9903,0.6514,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0229,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0412,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9767,0.9284,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0048,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0047,0.9663,0.1480,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0085,0.0000</t>
-  </si>
-  <si>
-    <t>0.0404,0.0135,0.9430,0.0001</t>
-  </si>
-  <si>
-    <t>0.1228,0.0696,0.7557,0.0005</t>
-  </si>
-  <si>
-    <t>0.0061,0.0540,0.9785,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9436,0.9163,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.3145,0.9874,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9887,0.5757,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9862,0.7044,0.0000</t>
-  </si>
-  <si>
-    <t>0.0415,0.0046,0.9619,0.0007</t>
-  </si>
-  <si>
-    <t>0.0730,0.0119,0.9232,0.0017</t>
-  </si>
-  <si>
-    <t>0.1741,0.0089,0.8401,0.0014</t>
-  </si>
-  <si>
-    <t>0.1188,0.0098,0.8892,0.0013</t>
-  </si>
-  <si>
-    <t>0.1669,0.0068,0.8429,0.0021</t>
-  </si>
-  <si>
-    <t>0.0319,0.0082,0.9655,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.8956,0.9416,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9845,0.8053,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9008,0.9703,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.3737,0.9923,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9202,0.9036,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.7555,0.9693,0.0000</t>
-  </si>
-  <si>
-    <t>0.4160,0.5813,0.0302,0.0005</t>
-  </si>
-  <si>
-    <t>0.2280,0.7370,0.0475,0.0006</t>
-  </si>
-  <si>
-    <t>0.1732,0.8328,0.0218,0.0003</t>
-  </si>
-  <si>
-    <t>0.4004,0.6228,0.0233,0.0004</t>
-  </si>
-  <si>
-    <t>0.3550,0.6683,0.0227,0.0004</t>
-  </si>
-  <si>
-    <t>0.3060,0.6834,0.0284,0.0004</t>
-  </si>
-  <si>
-    <t>0.2578,0.7303,0.0397,0.0006</t>
-  </si>
-  <si>
-    <t>0.2103,0.7544,0.0459,0.0006</t>
-  </si>
-  <si>
-    <t>0.5414,0.3195,0.0632,0.0009</t>
-  </si>
-  <si>
-    <t>0.3770,0.6136,0.0308,0.0005</t>
-  </si>
-  <si>
-    <t>0.4177,0.5780,0.0267,0.0005</t>
-  </si>
-  <si>
-    <t>0.6630,0.3752,0.0125,0.0002</t>
-  </si>
-  <si>
-    <t>0.2594,0.7539,0.0266,0.0005</t>
-  </si>
-  <si>
-    <t>0.4882,0.5113,0.0243,0.0004</t>
-  </si>
-  <si>
-    <t>0.4836,0.5346,0.0231,0.0004</t>
-  </si>
-  <si>
-    <t>0.4484,0.4339,0.0684,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0053,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0064,0.0293,0.9867,0.0001</t>
-  </si>
-  <si>
-    <t>0.0137,0.0191,0.9794,0.0001</t>
-  </si>
-  <si>
-    <t>0.0086,0.0441,0.9789,0.0001</t>
-  </si>
-  <si>
-    <t>0.0078,0.9835,0.0209,0.0001</t>
-  </si>
-  <si>
-    <t>0.0067,0.9776,0.0565,0.0001</t>
-  </si>
-  <si>
-    <t>0.0251,0.9541,0.0415,0.0002</t>
-  </si>
-  <si>
-    <t>0.0396,0.9257,0.0559,0.0002</t>
-  </si>
-  <si>
-    <t>0.0103,0.9568,0.1052,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.9952,0.0116,0.0000</t>
-  </si>
-  <si>
-    <t>0.0824,0.7962,0.1212,0.0004</t>
-  </si>
-  <si>
-    <t>0.0224,0.0336,0.9569,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.0133,0.9915,0.0000</t>
-  </si>
-  <si>
-    <t>0.0377,0.0563,0.9189,0.0003</t>
-  </si>
-  <si>
-    <t>0.0645,0.0365,0.8913,0.0004</t>
-  </si>
-  <si>
-    <t>0.0306,0.0173,0.9575,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.9984,0.0275,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9781,0.3471,0.0001</t>
-  </si>
-  <si>
-    <t>0.0112,0.8365,0.4256,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9967,0.1515,0.0000</t>
-  </si>
-  <si>
-    <t>0.0092,0.9769,0.0380,0.0001</t>
-  </si>
-  <si>
-    <t>0.0278,0.4617,0.7500,0.0003</t>
-  </si>
-  <si>
-    <t>0.0926,0.8582,0.0610,0.0004</t>
-  </si>
-  <si>
-    <t>0.1721,0.6859,0.1183,0.0008</t>
-  </si>
-  <si>
-    <t>0.4935,0.1040,0.2503,0.0010</t>
-  </si>
-  <si>
-    <t>0.5260,0.3895,0.0527,0.0008</t>
-  </si>
-  <si>
-    <t>0.3457,0.4809,0.1045,0.0009</t>
-  </si>
-  <si>
-    <t>0.5010,0.3728,0.0757,0.0012</t>
-  </si>
-  <si>
-    <t>0.2082,0.5636,0.1805,0.0010</t>
-  </si>
-  <si>
-    <t>0.3239,0.5024,0.1059,0.0009</t>
-  </si>
-  <si>
-    <t>0.3966,0.4413,0.0940,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.9086,0.9530,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8239,0.9846,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.2710,0.9732,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0575,0.9938,0.0000</t>
-  </si>
-  <si>
-    <t>0.0407,0.0206,0.9461,0.0003</t>
-  </si>
-  <si>
-    <t>0.0262,0.0395,0.9439,0.0001</t>
-  </si>
-  <si>
-    <t>0.0204,0.0133,0.9719,0.0001</t>
-  </si>
-  <si>
-    <t>0.1167,0.0363,0.8300,0.0005</t>
-  </si>
-  <si>
-    <t>0.1049,0.0113,0.8959,0.0010</t>
-  </si>
-  <si>
-    <t>0.0253,0.0046,0.9697,0.0037</t>
-  </si>
-  <si>
-    <t>0.0456,0.0101,0.9501,0.0009</t>
-  </si>
-  <si>
-    <t>0.1325,0.0067,0.8731,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.4753,0.0000</t>
-  </si>
-  <si>
-    <t>0.2746,0.5242,0.1475,0.0011</t>
-  </si>
-  <si>
-    <t>0.0260,0.4737,0.7509,0.0004</t>
-  </si>
-  <si>
-    <t>0.4794,0.2513,0.1328,0.0011</t>
-  </si>
-  <si>
-    <t>0.0583,0.8376,0.1277,0.0004</t>
-  </si>
-  <si>
-    <t>0.3093,0.1393,0.4242,0.0013</t>
-  </si>
-  <si>
-    <t>0.4212,0.0189,0.5366,0.0011</t>
-  </si>
-  <si>
-    <t>0.4443,0.2494,0.1582,0.0010</t>
-  </si>
-  <si>
-    <t>0.0214,0.0489,0.9483,0.0001</t>
-  </si>
-  <si>
-    <t>0.3527,0.0147,0.6253,0.0008</t>
-  </si>
-  <si>
-    <t>0.6305,0.0292,0.2662,0.0018</t>
-  </si>
-  <si>
-    <t>0.0650,0.5825,0.4377,0.0007</t>
-  </si>
-  <si>
-    <t>0.2917,0.1017,0.4892,0.0012</t>
-  </si>
-  <si>
-    <t>0.3431,0.0404,0.5471,0.0009</t>
-  </si>
-  <si>
-    <t>0.0291,0.2746,0.8348,0.0004</t>
-  </si>
-  <si>
-    <t>0.2182,0.0216,0.7177,0.0004</t>
-  </si>
-  <si>
-    <t>0.2162,0.0747,0.6409,0.0009</t>
-  </si>
-  <si>
-    <t>0.2603,0.6110,0.0855,0.0009</t>
-  </si>
-  <si>
-    <t>0.4275,0.3783,0.1173,0.0014</t>
-  </si>
-  <si>
-    <t>0.5408,0.3586,0.0486,0.0007</t>
-  </si>
-  <si>
-    <t>0.4318,0.3971,0.0888,0.0010</t>
-  </si>
-  <si>
-    <t>0.4132,0.1533,0.2770,0.0009</t>
-  </si>
-  <si>
-    <t>0.4430,0.4671,0.0486,0.0006</t>
-  </si>
-  <si>
-    <t>0.5392,0.3114,0.0636,0.0006</t>
-  </si>
-  <si>
-    <t>0.4797,0.3546,0.0782,0.0008</t>
-  </si>
-  <si>
-    <t>0.0192,0.9529,0.0764,0.0002</t>
-  </si>
-  <si>
-    <t>0.0777,0.8908,0.0402,0.0003</t>
-  </si>
-  <si>
-    <t>0.0874,0.8438,0.0668,0.0004</t>
-  </si>
-  <si>
-    <t>0.0207,0.3928,0.8201,0.0003</t>
-  </si>
-  <si>
-    <t>0.1125,0.8269,0.0571,0.0004</t>
-  </si>
-  <si>
-    <t>0.0771,0.7809,0.2092,0.0007</t>
-  </si>
-  <si>
-    <t>0.2353,0.5235,0.1701,0.0009</t>
-  </si>
-  <si>
-    <t>0.0925,0.8330,0.0704,0.0004</t>
-  </si>
-  <si>
-    <t>0.0021,0.0560,0.9922,0.0000</t>
-  </si>
-  <si>
-    <t>0.1050,0.1840,0.6527,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0051,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.1383,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0124,0.0073,0.9861,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.3106,0.9740,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0208,0.9971,0.0000</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.1048,0.0253,0.8580,0.0004</t>
+  </si>
+  <si>
+    <t>0.0870,0.0087,0.9132,0.0011</t>
+  </si>
+  <si>
+    <t>0.4057,0.0108,0.5797,0.0018</t>
+  </si>
+  <si>
+    <t>0.0996,0.0097,0.8976,0.0009</t>
+  </si>
+  <si>
+    <t>0.4943,0.5246,0.0193,0.0003</t>
+  </si>
+  <si>
+    <t>0.4319,0.5605,0.0318,0.0006</t>
+  </si>
+  <si>
+    <t>0.2806,0.7067,0.0346,0.0005</t>
+  </si>
+  <si>
+    <t>0.5004,0.5266,0.0199,0.0003</t>
+  </si>
+  <si>
+    <t>0.3357,0.7082,0.0187,0.0004</t>
+  </si>
+  <si>
+    <t>0.4182,0.5726,0.0287,0.0005</t>
+  </si>
+  <si>
+    <t>0.4826,0.5444,0.0204,0.0004</t>
+  </si>
+  <si>
+    <t>0.5682,0.4390,0.0223,0.0004</t>
+  </si>
+  <si>
+    <t>0.0629,0.0481,0.8933,0.0005</t>
+  </si>
+  <si>
+    <t>0.0090,0.0172,0.9843,0.0001</t>
+  </si>
+  <si>
+    <t>0.0268,0.0353,0.9499,0.0002</t>
+  </si>
+  <si>
+    <t>0.0091,0.0224,0.9837,0.0001</t>
+  </si>
+  <si>
+    <t>0.0545,0.0160,0.9303,0.0002</t>
+  </si>
+  <si>
+    <t>0.0031,0.9915,0.0257,0.0000</t>
+  </si>
+  <si>
+    <t>0.0050,0.9802,0.0715,0.0001</t>
+  </si>
+  <si>
+    <t>0.0303,0.8861,0.1852,0.0003</t>
+  </si>
+  <si>
+    <t>0.0051,0.9836,0.0526,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9976,0.0110,0.0000</t>
+  </si>
+  <si>
+    <t>0.0421,0.0188,0.9467,0.0002</t>
+  </si>
+  <si>
+    <t>0.0069,0.0161,0.9903,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0062,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0044,0.0146,0.9931,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.0125,0.9927,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0275,0.9912,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0052,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0987,0.4298,0.4529,0.0006</t>
+  </si>
+  <si>
+    <t>0.0893,0.1449,0.7460,0.0006</t>
+  </si>
+  <si>
+    <t>0.0023,0.0219,0.9940,0.0000</t>
+  </si>
+  <si>
+    <t>0.0276,0.5842,0.5772,0.0004</t>
+  </si>
+  <si>
+    <t>0.0914,0.1823,0.7325,0.0007</t>
+  </si>
+  <si>
+    <t>0.1104,0.1597,0.7085,0.0007</t>
+  </si>
+  <si>
+    <t>0.0633,0.8519,0.1105,0.0004</t>
+  </si>
+  <si>
+    <t>0.0196,0.8412,0.3911,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9804,0.7551,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.1392,0.9925,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.1750,0.9958,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0171,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.7500,0.9748,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9841,0.2772,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0131,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0936,0.0433,0.8611,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.9970,0.0738,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9795,0.5053,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9988,0.0218,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.7884,0.9541,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.1928,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0059,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0040,0.9983,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.0020,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0014,0.0180,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0258,0.0568,0.9420,0.0003</t>
-  </si>
-  <si>
-    <t>0.0087,0.0170,0.9853,0.0001</t>
-  </si>
-  <si>
-    <t>0.0255,0.1953,0.8771,0.0003</t>
-  </si>
-  <si>
-    <t>0.0344,0.0472,0.9275,0.0002</t>
-  </si>
-  <si>
-    <t>0.0104,0.0235,0.9806,0.0001</t>
-  </si>
-  <si>
-    <t>0.0181,0.0234,0.9686,0.0001</t>
-  </si>
-  <si>
-    <t>0.0494,0.0194,0.9338,0.0003</t>
-  </si>
-  <si>
-    <t>0.0387,0.0350,0.9338,0.0002</t>
-  </si>
-  <si>
-    <t>0.0767,0.8722,0.0630,0.0003</t>
-  </si>
-  <si>
-    <t>0.0459,0.9249,0.0390,0.0002</t>
-  </si>
-  <si>
-    <t>0.0346,0.9474,0.0283,0.0001</t>
-  </si>
-  <si>
-    <t>0.0459,0.9408,0.0235,0.0002</t>
-  </si>
-  <si>
-    <t>0.0835,0.8504,0.0656,0.0003</t>
-  </si>
-  <si>
-    <t>0.1158,0.0330,0.8329,0.0006</t>
-  </si>
-  <si>
-    <t>0.0428,0.0295,0.9360,0.0003</t>
-  </si>
-  <si>
-    <t>0.0206,0.0247,0.9664,0.0002</t>
-  </si>
-  <si>
-    <t>0.0168,0.0129,0.9783,0.0001</t>
-  </si>
-  <si>
-    <t>0.0635,0.0097,0.9341,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0160,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.1752,0.9892,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.1197,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0329,0.9935,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0805,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.3407,0.6457,0.0396,0.0008</t>
-  </si>
-  <si>
-    <t>0.3806,0.6091,0.0313,0.0005</t>
-  </si>
-  <si>
-    <t>0.2330,0.7452,0.0476,0.0008</t>
-  </si>
-  <si>
-    <t>0.2931,0.7191,0.0256,0.0004</t>
-  </si>
-  <si>
-    <t>0.3496,0.6247,0.0346,0.0005</t>
-  </si>
-  <si>
-    <t>0.3305,0.6174,0.0515,0.0007</t>
-  </si>
-  <si>
-    <t>0.2604,0.7306,0.0305,0.0005</t>
-  </si>
-  <si>
-    <t>0.5367,0.4117,0.0405,0.0008</t>
-  </si>
-  <si>
-    <t>0.0052,0.0265,0.9886,0.0001</t>
-  </si>
-  <si>
-    <t>0.0964,0.1054,0.7798,0.0007</t>
-  </si>
-  <si>
-    <t>0.2112,0.0385,0.7109,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0048,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0036,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0249,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0041,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0147,0.9956,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0052,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0210,0.9969,0.0000</t>
-  </si>
-  <si>
-    <t>0.0070,0.0229,0.9852,0.0001</t>
-  </si>
-  <si>
-    <t>0.0273,0.0341,0.9522,0.0002</t>
-  </si>
-  <si>
-    <t>0.0262,0.0111,0.9671,0.0001</t>
-  </si>
-  <si>
-    <t>0.0361,0.0334,0.9394,0.0002</t>
-  </si>
-  <si>
-    <t>0.2114,0.7884,0.0349,0.0006</t>
-  </si>
-  <si>
-    <t>0.3796,0.5762,0.0432,0.0007</t>
-  </si>
-  <si>
-    <t>0.5398,0.4835,0.0196,0.0004</t>
-  </si>
-  <si>
-    <t>0.2831,0.7132,0.0292,0.0004</t>
-  </si>
-  <si>
-    <t>0.2632,0.7439,0.0282,0.0004</t>
-  </si>
-  <si>
-    <t>0.2361,0.7439,0.0398,0.0006</t>
-  </si>
-  <si>
-    <t>0.2180,0.7679,0.0343,0.0005</t>
-  </si>
-  <si>
-    <t>0.4913,0.5427,0.0234,0.0005</t>
-  </si>
-  <si>
-    <t>0.0033,0.0915,0.9852,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0659,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0795,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0608,0.9899,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0153,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0042,0.0240,0.9911,0.0001</t>
-  </si>
-  <si>
-    <t>0.0180,0.0157,0.9757,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.0531,0.9913,0.0000</t>
-  </si>
-  <si>
-    <t>0.3121,0.0216,0.6305,0.0006</t>
-  </si>
-  <si>
-    <t>0.0575,0.0185,0.9247,0.0013</t>
-  </si>
-  <si>
-    <t>0.3242,0.0160,0.6553,0.0017</t>
-  </si>
-  <si>
-    <t>0.1098,0.0033,0.8879,0.0056</t>
-  </si>
-  <si>
-    <t>0.1180,0.0116,0.8842,0.0022</t>
-  </si>
-  <si>
-    <t>0.1938,0.0279,0.7327,0.0009</t>
+    <t>0.0017,0.0384,0.9949,0.0000</t>
+  </si>
+  <si>
+    <t>0.1842,0.7591,0.0645,0.0008</t>
+  </si>
+  <si>
+    <t>0.2971,0.1987,0.3704,0.0010</t>
+  </si>
+  <si>
+    <t>0.2215,0.7361,0.0426,0.0005</t>
+  </si>
+  <si>
+    <t>0.0054,0.0578,0.9844,0.0001</t>
+  </si>
+  <si>
+    <t>0.4700,0.3945,0.0757,0.0009</t>
+  </si>
+  <si>
+    <t>0.2502,0.7475,0.0301,0.0004</t>
+  </si>
+  <si>
+    <t>0.2192,0.7103,0.0612,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9865,0.7473,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.1664,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.1309,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.7758,0.9886,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0147,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9860,0.1602,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0092,0.0000</t>
+  </si>
+  <si>
+    <t>0.0649,0.0208,0.9073,0.0002</t>
+  </si>
+  <si>
+    <t>0.0956,0.0735,0.7948,0.0005</t>
+  </si>
+  <si>
+    <t>0.0090,0.0476,0.9747,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9314,0.9539,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.8558,0.9381,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9946,0.3221,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9346,0.9509,0.0000</t>
+  </si>
+  <si>
+    <t>0.0334,0.0060,0.9684,0.0004</t>
+  </si>
+  <si>
+    <t>0.0941,0.0075,0.9009,0.0036</t>
+  </si>
+  <si>
+    <t>0.1410,0.0109,0.8598,0.0014</t>
+  </si>
+  <si>
+    <t>0.1455,0.0071,0.8610,0.0020</t>
+  </si>
+  <si>
+    <t>0.0900,0.0072,0.9163,0.0013</t>
+  </si>
+  <si>
+    <t>0.0243,0.0113,0.9702,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.9747,0.8355,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9886,0.7493,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.7272,0.9637,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.4165,0.9798,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.8905,0.9494,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.6474,0.9637,0.0000</t>
+  </si>
+  <si>
+    <t>0.3957,0.6016,0.0271,0.0004</t>
+  </si>
+  <si>
+    <t>0.3575,0.6415,0.0293,0.0005</t>
+  </si>
+  <si>
+    <t>0.1567,0.8493,0.0205,0.0003</t>
+  </si>
+  <si>
+    <t>0.3583,0.6170,0.0353,0.0006</t>
+  </si>
+  <si>
+    <t>0.3388,0.6806,0.0228,0.0004</t>
+  </si>
+  <si>
+    <t>0.5343,0.4939,0.0177,0.0003</t>
+  </si>
+  <si>
+    <t>0.3939,0.5805,0.0373,0.0006</t>
+  </si>
+  <si>
+    <t>0.2411,0.7435,0.0349,0.0005</t>
+  </si>
+  <si>
+    <t>0.5793,0.3048,0.0516,0.0008</t>
+  </si>
+  <si>
+    <t>0.4133,0.5566,0.0381,0.0006</t>
+  </si>
+  <si>
+    <t>0.4768,0.5372,0.0208,0.0003</t>
+  </si>
+  <si>
+    <t>0.5766,0.4612,0.0167,0.0003</t>
+  </si>
+  <si>
+    <t>0.3831,0.6749,0.0168,0.0003</t>
+  </si>
+  <si>
+    <t>0.4054,0.5954,0.0276,0.0005</t>
+  </si>
+  <si>
+    <t>0.5123,0.4800,0.0270,0.0005</t>
+  </si>
+  <si>
+    <t>0.6370,0.3507,0.0233,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0029,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0160,0.9955,0.0000</t>
+  </si>
+  <si>
+    <t>0.0223,0.0291,0.9655,0.0002</t>
+  </si>
+  <si>
+    <t>0.0067,0.0153,0.9890,0.0001</t>
+  </si>
+  <si>
+    <t>0.0046,0.9897,0.0177,0.0000</t>
+  </si>
+  <si>
+    <t>0.0055,0.9889,0.0157,0.0000</t>
+  </si>
+  <si>
+    <t>0.0196,0.9547,0.0531,0.0001</t>
+  </si>
+  <si>
+    <t>0.0229,0.9581,0.0378,0.0001</t>
+  </si>
+  <si>
+    <t>0.0130,0.9423,0.1408,0.0002</t>
+  </si>
+  <si>
+    <t>0.0032,0.9916,0.0165,0.0000</t>
+  </si>
+  <si>
+    <t>0.0737,0.7583,0.1836,0.0005</t>
+  </si>
+  <si>
+    <t>0.0429,0.0197,0.9367,0.0002</t>
+  </si>
+  <si>
+    <t>0.0049,0.0184,0.9899,0.0000</t>
+  </si>
+  <si>
+    <t>0.0362,0.0367,0.9338,0.0002</t>
+  </si>
+  <si>
+    <t>0.0488,0.1562,0.8041,0.0005</t>
+  </si>
+  <si>
+    <t>0.0738,0.0316,0.8945,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.9956,0.1237,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9952,0.1152,0.0000</t>
+  </si>
+  <si>
+    <t>0.0300,0.5674,0.6028,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.0684,0.0000</t>
+  </si>
+  <si>
+    <t>0.0103,0.9748,0.0397,0.0001</t>
+  </si>
+  <si>
+    <t>0.0331,0.8188,0.2779,0.0003</t>
+  </si>
+  <si>
+    <t>0.0509,0.9031,0.0760,0.0003</t>
+  </si>
+  <si>
+    <t>0.1071,0.7827,0.1105,0.0006</t>
+  </si>
+  <si>
+    <t>0.5828,0.1518,0.1212,0.0010</t>
+  </si>
+  <si>
+    <t>0.3039,0.5245,0.1170,0.0013</t>
+  </si>
+  <si>
+    <t>0.2979,0.2989,0.2949,0.0013</t>
+  </si>
+  <si>
+    <t>0.5010,0.3592,0.0700,0.0008</t>
+  </si>
+  <si>
+    <t>0.1382,0.6875,0.1641,0.0007</t>
+  </si>
+  <si>
+    <t>0.3119,0.6404,0.0501,0.0007</t>
+  </si>
+  <si>
+    <t>0.4054,0.4592,0.0813,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.6281,0.9854,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.7380,0.9808,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.1007,0.9933,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.1306,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0376,0.0520,0.9181,0.0002</t>
+  </si>
+  <si>
+    <t>0.0315,0.0719,0.9154,0.0002</t>
+  </si>
+  <si>
+    <t>0.0269,0.0105,0.9653,0.0001</t>
+  </si>
+  <si>
+    <t>0.0447,0.0346,0.9248,0.0003</t>
+  </si>
+  <si>
+    <t>0.1010,0.0121,0.9030,0.0006</t>
+  </si>
+  <si>
+    <t>0.0359,0.0036,0.9587,0.0040</t>
+  </si>
+  <si>
+    <t>0.0455,0.0052,0.9538,0.0016</t>
+  </si>
+  <si>
+    <t>0.2066,0.0112,0.7915,0.0016</t>
+  </si>
+  <si>
+    <t>0.0001,0.9860,0.7319,0.0000</t>
+  </si>
+  <si>
+    <t>0.3513,0.3772,0.1685,0.0013</t>
+  </si>
+  <si>
+    <t>0.0209,0.8290,0.3515,0.0003</t>
+  </si>
+  <si>
+    <t>0.4291,0.1479,0.2671,0.0011</t>
+  </si>
+  <si>
+    <t>0.0761,0.8315,0.0972,0.0004</t>
+  </si>
+  <si>
+    <t>0.6192,0.1147,0.1344,0.0013</t>
+  </si>
+  <si>
+    <t>0.3587,0.0241,0.5971,0.0012</t>
+  </si>
+  <si>
+    <t>0.5808,0.1877,0.1006,0.0008</t>
+  </si>
+  <si>
+    <t>0.0530,0.0373,0.9068,0.0003</t>
+  </si>
+  <si>
+    <t>0.4871,0.0146,0.4744,0.0007</t>
+  </si>
+  <si>
+    <t>0.5670,0.0678,0.2531,0.0013</t>
+  </si>
+  <si>
+    <t>0.0582,0.3760,0.6709,0.0006</t>
+  </si>
+  <si>
+    <t>0.1943,0.1663,0.5458,0.0010</t>
+  </si>
+  <si>
+    <t>0.2823,0.0396,0.6015,0.0007</t>
+  </si>
+  <si>
+    <t>0.0456,0.1233,0.8639,0.0004</t>
+  </si>
+  <si>
+    <t>0.3453,0.0768,0.4429,0.0010</t>
+  </si>
+  <si>
+    <t>0.1738,0.0521,0.7338,0.0007</t>
+  </si>
+  <si>
+    <t>0.3540,0.3443,0.1752,0.0011</t>
+  </si>
+  <si>
+    <t>0.3762,0.4467,0.1105,0.0011</t>
+  </si>
+  <si>
+    <t>0.4837,0.4365,0.0477,0.0007</t>
+  </si>
+  <si>
+    <t>0.5904,0.2342,0.0682,0.0008</t>
+  </si>
+  <si>
+    <t>0.6129,0.2322,0.0576,0.0006</t>
+  </si>
+  <si>
+    <t>0.3505,0.5697,0.0562,0.0007</t>
+  </si>
+  <si>
+    <t>0.4565,0.3592,0.0889,0.0009</t>
+  </si>
+  <si>
+    <t>0.5568,0.2133,0.1043,0.0010</t>
+  </si>
+  <si>
+    <t>0.0340,0.8991,0.1357,0.0003</t>
+  </si>
+  <si>
+    <t>0.0773,0.8930,0.0359,0.0003</t>
+  </si>
+  <si>
+    <t>0.0647,0.8642,0.0819,0.0003</t>
+  </si>
+  <si>
+    <t>0.0258,0.7932,0.3880,0.0003</t>
+  </si>
+  <si>
+    <t>0.2447,0.6599,0.0788,0.0008</t>
+  </si>
+  <si>
+    <t>0.0565,0.7387,0.3490,0.0006</t>
+  </si>
+  <si>
+    <t>0.3259,0.4953,0.1109,0.0009</t>
+  </si>
+  <si>
+    <t>0.1419,0.7274,0.1157,0.0006</t>
+  </si>
+  <si>
+    <t>0.0015,0.0229,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.1276,0.1716,0.6583,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0070,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0887,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0051,0.0070,0.9933,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.1524,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0176,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0048,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0170,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0262,0.0703,0.9318,0.0002</t>
+  </si>
+  <si>
+    <t>0.0111,0.0093,0.9849,0.0000</t>
+  </si>
+  <si>
+    <t>0.0517,0.1028,0.8579,0.0004</t>
+  </si>
+  <si>
+    <t>0.0276,0.0546,0.9358,0.0002</t>
+  </si>
+  <si>
+    <t>0.0369,0.0290,0.9426,0.0002</t>
+  </si>
+  <si>
+    <t>0.0430,0.0353,0.9285,0.0003</t>
+  </si>
+  <si>
+    <t>0.1303,0.0324,0.8219,0.0007</t>
+  </si>
+  <si>
+    <t>0.0313,0.1170,0.9011,0.0004</t>
+  </si>
+  <si>
+    <t>0.0954,0.8371,0.0802,0.0005</t>
+  </si>
+  <si>
+    <t>0.0225,0.9564,0.0414,0.0001</t>
+  </si>
+  <si>
+    <t>0.1022,0.8566,0.0447,0.0003</t>
+  </si>
+  <si>
+    <t>0.2133,0.7531,0.0410,0.0005</t>
+  </si>
+  <si>
+    <t>0.1072,0.8503,0.0466,0.0003</t>
+  </si>
+  <si>
+    <t>0.0387,0.0541,0.9133,0.0003</t>
+  </si>
+  <si>
+    <t>0.0382,0.0166,0.9514,0.0002</t>
+  </si>
+  <si>
+    <t>0.0332,0.0303,0.9462,0.0002</t>
+  </si>
+  <si>
+    <t>0.0166,0.0184,0.9747,0.0001</t>
+  </si>
+  <si>
+    <t>0.0769,0.0202,0.9049,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.0246,0.9944,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0232,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.1054,0.9965,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0247,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.1204,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.3133,0.6768,0.0371,0.0007</t>
+  </si>
+  <si>
+    <t>0.3069,0.6102,0.0627,0.0007</t>
+  </si>
+  <si>
+    <t>0.3771,0.6371,0.0308,0.0006</t>
+  </si>
+  <si>
+    <t>0.3403,0.6500,0.0325,0.0005</t>
+  </si>
+  <si>
+    <t>0.3036,0.6984,0.0315,0.0006</t>
+  </si>
+  <si>
+    <t>0.4602,0.5347,0.0307,0.0007</t>
+  </si>
+  <si>
+    <t>0.3727,0.5193,0.0624,0.0007</t>
+  </si>
+  <si>
+    <t>0.5461,0.3384,0.0568,0.0008</t>
+  </si>
+  <si>
+    <t>0.0232,0.0555,0.9503,0.0002</t>
+  </si>
+  <si>
+    <t>0.1325,0.1637,0.6254,0.0008</t>
+  </si>
+  <si>
+    <t>0.1971,0.0467,0.7011,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0041,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0075,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0253,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0037,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0083,0.0189,0.9856,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0047,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0081,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.0051,0.9949,0.0000</t>
+  </si>
+  <si>
+    <t>0.0184,0.0260,0.9685,0.0002</t>
+  </si>
+  <si>
+    <t>0.0074,0.0134,0.9879,0.0001</t>
+  </si>
+  <si>
+    <t>0.0490,0.0319,0.9266,0.0003</t>
+  </si>
+  <si>
+    <t>0.2601,0.7487,0.0282,0.0005</t>
+  </si>
+  <si>
+    <t>0.3576,0.6344,0.0308,0.0005</t>
+  </si>
+  <si>
+    <t>0.4643,0.5132,0.0307,0.0005</t>
+  </si>
+  <si>
+    <t>0.2777,0.6967,0.0387,0.0005</t>
+  </si>
+  <si>
+    <t>0.2047,0.7672,0.0410,0.0006</t>
+  </si>
+  <si>
+    <t>0.3725,0.6057,0.0323,0.0005</t>
+  </si>
+  <si>
+    <t>0.2786,0.7216,0.0305,0.0005</t>
+  </si>
+  <si>
+    <t>0.4384,0.5800,0.0293,0.0006</t>
+  </si>
+  <si>
+    <t>0.0032,0.0863,0.9869,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0096,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0108,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.0252,0.9930,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0108,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0177,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.0263,0.9890,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0355,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.3292,0.0280,0.6114,0.0009</t>
+  </si>
+  <si>
+    <t>0.0929,0.0229,0.8788,0.0008</t>
+  </si>
+  <si>
+    <t>0.1646,0.0072,0.8405,0.0019</t>
+  </si>
+  <si>
+    <t>0.0810,0.0042,0.9264,0.0019</t>
+  </si>
+  <si>
+    <t>0.1263,0.0099,0.8750,0.0027</t>
+  </si>
+  <si>
+    <t>0.1073,0.0081,0.8891,0.0002</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1962,7 @@
         <v>261</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>261</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1990,7 @@
         <v>261</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>261</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>262</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>262</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>262</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,10 +2057,10 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>262</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>262</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>262</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,10 +2113,10 @@
         <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2130,7 @@
         <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2186,7 @@
         <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2365,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2382,7 @@
         <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>261</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2438,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2452,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2578,7 @@
         <v>261</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,10 +2603,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>262</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,10 +2729,10 @@
         <v>259</v>
       </c>
       <c r="C57" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>262</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,10 +2771,10 @@
         <v>259</v>
       </c>
       <c r="C60" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>262</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>262</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2914,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2928,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2967,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2981,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>261</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>261</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>261</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>261</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>261</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>261</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3138,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>262</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>262</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>262</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>262</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>262</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,10 +3247,10 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>262</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>262</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>262</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>262</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>262</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>262</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,10 +3373,10 @@
         <v>259</v>
       </c>
       <c r="C103" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3432,7 @@
         <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3558,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3586,7 @@
         <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3600,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3614,7 @@
         <v>261</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3653,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3695,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3712,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>262</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,10 +3751,10 @@
         <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,10 +3765,10 @@
         <v>259</v>
       </c>
       <c r="C131" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>262</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>262</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,10 +3821,10 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3894,7 @@
         <v>261</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3908,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3936,7 @@
         <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>261</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>261</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>261</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>261</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4003,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,10 +4017,10 @@
         <v>259</v>
       </c>
       <c r="C149" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4031,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,10 +4045,10 @@
         <v>259</v>
       </c>
       <c r="C151" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4062,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4090,7 @@
         <v>261</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4129,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4157,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,10 +4171,10 @@
         <v>259</v>
       </c>
       <c r="C160" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>261</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4202,7 @@
         <v>261</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4213,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>261</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,10 +4241,10 @@
         <v>259</v>
       </c>
       <c r="C165" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,10 +4255,10 @@
         <v>259</v>
       </c>
       <c r="C166" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,10 +4269,10 @@
         <v>259</v>
       </c>
       <c r="C167" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,10 +4311,10 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,10 +4325,10 @@
         <v>259</v>
       </c>
       <c r="C171" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4356,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4370,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>262</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>262</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,10 +4437,10 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4454,7 @@
         <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>261</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4622,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4636,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4650,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4664,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4678,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4692,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4706,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4776,7 @@
         <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4790,7 @@
         <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>261</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4818,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4832,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>262</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>262</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>262</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>262</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>262</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>262</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>262</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>261</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5182,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5196,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>261</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>262</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>262</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,10 +5249,10 @@
         <v>259</v>
       </c>
       <c r="C237" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>262</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>262</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>262</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>262</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>262</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5448,7 @@
         <v>261</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5462,7 @@
         <v>261</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>261</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>261</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>261</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5518,7 @@
         <v>261</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
